--- a/survey_templates/040_grilled_wings_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/040_grilled_wings_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>general_info</t>
+          <t>general_info_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>General Info</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rating_taste</t>
+          <t>general_info_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How would you rate the taste?</t>
+          <t>How long did it take to receive your order?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rating_presentation</t>
+          <t>taste</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How would you rate the presentation?</t>
+          <t>How would you rate the taste?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating_service</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How would you rate the service?</t>
+          <t>How would you rate the presentation?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What would you recommend to us?</t>
+          <t>How would you rate the service?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,70 +646,70 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rating_quality</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How would you rate the quality of the product?</t>
+          <t>What would you recommend to us?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating_time</t>
+          <t>food_quality_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How long did it take to receive your order?</t>
+          <t>How would you rate the quality of the food?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rating_time_2</t>
+          <t>food_quality_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How long did it take to receive your order?</t>
+          <t>Food Quality 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rating_food</t>
+          <t>beverage_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How would you rate the food quality?</t>
+          <t>How would you rate the quality of the beverage?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rating_food_2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How would you rate the food quality?</t>
+          <t>Additional comments?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rating_food_3</t>
+          <t>rating_beverage_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How would you rate the food quality?</t>
+          <t>Rating Beverage 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rating_food_4</t>
+          <t>rating_beverage_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How would you rate the food quality?</t>
+          <t>Rating Beverage 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rating_beverage</t>
+          <t>rating_beverage_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How would you rate the beverage?</t>
+          <t>Rating Beverage 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,108 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rating_food_5</t>
+          <t>rating_beverage_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How would you rate the food quality?</t>
+          <t>Rating Beverage 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rating_beverage_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>How would you rate the beverage?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rating_beverage_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How would you rate the beverage?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rating_beverage_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How would you rate the beverage?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rating_beverage_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How would you rate the beverage?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Recommend</t>
         </is>
       </c>
     </row>
@@ -1010,240 +918,240 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>not_recommend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Not Recommend</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>recommendation_choices</t>
+          <t>food_quality_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rating_food_choices</t>
+          <t>food_quality_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rating_food_choices</t>
+          <t>food_quality_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rating_food_2_choices</t>
+          <t>food_quality_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rating_food_2_choices</t>
+          <t>food_quality_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rating_food_2_choices</t>
+          <t>beverage_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rating_food_3_choices</t>
+          <t>beverage_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rating_food_3_choices</t>
+          <t>rating_beverage_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rating_food_4_choices</t>
+          <t>rating_beverage_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rating_food_4_choices</t>
+          <t>rating_beverage_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rating_beverage_choices</t>
+          <t>rating_beverage_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rating_beverage_choices</t>
+          <t>rating_beverage_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rating_beverage_choices</t>
+          <t>rating_beverage_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rating_food_5_choices</t>
+          <t>rating_beverage_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1260,151 +1168,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rating_food_5_choices</t>
+          <t>rating_beverage_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>rating_beverage_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>rating_beverage_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>rating_beverage_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>rating_beverage_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>rating_beverage_4_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>rating_beverage_4_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>rating_beverage_5_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>rating_beverage_5_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
